--- a/outputs/03_问题3/表5_指定日期NTU预测结果.xlsx
+++ b/outputs/03_问题3/表5_指定日期NTU预测结果.xlsx
@@ -436,17 +436,17 @@
   <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
